--- a/Cambiar Lotes/ListaMuestras.xlsx
+++ b/Cambiar Lotes/ListaMuestras.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,171 +457,446 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1481184</v>
+        <v>2138288</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ERROR RECIPIENTES</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1547892</v>
+        <v>1958147</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1610657</v>
+        <v>1958148</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610658</v>
+        <v>1958149</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ERROR RECIPIENTES</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1687012</v>
+        <v>2114484</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SALTADA</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1809251</v>
+        <v>2114486</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ERROR RECIPIENTES</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1809254</v>
+        <v>2114488</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ERROR RECIPIENTES</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1855648</v>
+        <v>2114489</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ERROR RECIPIENTES</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1855651</v>
+        <v>2114490</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1855652</v>
+        <v>2114491</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1855653</v>
+        <v>2114493</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1870924</v>
+        <v>2114495</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1966870</v>
+        <v>2114497</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2055395</v>
+        <v>2114499</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2055516</v>
+        <v>2114503</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2088247</v>
+        <v>2114504</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2115672</v>
+        <v>2136211</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2115673</v>
+        <v>1958156</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2115674</v>
+        <v>1958157</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2132568</v>
+        <v>1958158</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2132569</v>
+        <v>2132753</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2132570</v>
+        <v>2132774</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2133044</v>
+        <v>2076107</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2133045</v>
+        <v>2076108</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2133046</v>
+        <v>2076110</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2076111</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2076112</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2076113</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2076114</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2076115</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2076116</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2076117</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2076118</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2083654</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2106082</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2106084</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2106085</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2130705</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1779986</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1958155</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1958160</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1958164</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2127445</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2126227</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B26"/>
+  <autoFilter ref="A1:B45"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Cambiar Lotes/ListaMuestras.xlsx
+++ b/Cambiar Lotes/ListaMuestras.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,446 +457,86 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2138288</v>
+        <v>1587258</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EDITADO</t>
+          <t>LISTA REPROCESADA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1958147</v>
+        <v>1587257</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EDITADO</t>
+          <t>LISTA REPROCESADA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1958148</v>
+        <v>1587255</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EDITADO</t>
+          <t>LISTA REPROCESADA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1958149</v>
+        <v>1587249</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EDITADO</t>
+          <t>LISTA REPROCESADA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2114484</v>
+        <v>1587242</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EDITADO</t>
+          <t>LISTA REPROCESADA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2114486</v>
+        <v>1587236</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EDITADO</t>
+          <t>LISTA REPROCESADA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2114488</v>
+        <v>1587232</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EDITADO</t>
+          <t>LISTA REPROCESADA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2114489</v>
+        <v>1587231</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2114490</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2114491</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2114493</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2114495</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2114497</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2114499</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2114503</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2114504</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2136211</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1958156</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1958157</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1958158</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2132753</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2132774</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2076107</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2076108</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2076110</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2076111</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2076112</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2076113</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>2076114</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>2076115</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>2076116</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>2076117</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>2076118</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>2083654</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>2106082</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>2106084</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>2106085</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>2130705</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1779986</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>1958155</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1958160</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>1958164</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>2127445</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>2126227</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
+          <t>LISTA REPROCESADA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B45"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Cambiar Lotes/ListaMuestras.xlsx
+++ b/Cambiar Lotes/ListaMuestras.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,86 +457,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1587258</v>
+        <v>2101000</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>PARA DESCARGAR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1587257</v>
+        <v>2112688</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>PARA DESCARGAR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1587255</v>
+        <v>2112049</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>PARA DESCARGAR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1587249</v>
+        <v>2148293</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1587242</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1587236</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1587232</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1587231</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
+          <t>PARA DESCARGAR</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Cambiar Lotes/ListaMuestras.xlsx
+++ b/Cambiar Lotes/ListaMuestras.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B96"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2173201</v>
+        <v>2202170</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -467,7 +467,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2173203</v>
+        <v>2213618</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -477,7 +477,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2173205</v>
+        <v>2115271</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -487,7 +487,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2173207</v>
+        <v>2151815</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2157918</v>
+        <v>2184605</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2175836</v>
+        <v>2184606</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2175837</v>
+        <v>2184611</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2175838</v>
+        <v>2191618</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2175839</v>
+        <v>2191620</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2177460</v>
+        <v>2217641</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2182598</v>
+        <v>2122289</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2182600</v>
+        <v>2137849</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2182602</v>
+        <v>2137850</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2182604</v>
+        <v>2138386</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2184575</v>
+        <v>2138409</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2184576</v>
+        <v>2138449</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2124041</v>
+        <v>2138451</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2149232</v>
+        <v>2138990</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2149233</v>
+        <v>2139310</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2149234</v>
+        <v>2146959</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2149235</v>
+        <v>2146960</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2149236</v>
+        <v>2146964</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2149237</v>
+        <v>2146965</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2149238</v>
+        <v>2180906</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2162519</v>
+        <v>2184612</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2162521</v>
+        <v>2184613</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2162522</v>
+        <v>2184614</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2170519</v>
+        <v>2200250</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2171304</v>
+        <v>2201781</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2181937</v>
+        <v>2201784</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2181945</v>
+        <v>2203865</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2181949</v>
+        <v>2209239</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2184577</v>
+        <v>2210614</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2185852</v>
+        <v>2210776</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2185853</v>
+        <v>2214776</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -807,17 +807,17 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2185854</v>
+        <v>2214781</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EDITADO</t>
+          <t>SIN METODO</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2185855</v>
+        <v>2114536</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2187213</v>
+        <v>2146961</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2188676</v>
+        <v>2146962</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2124033</v>
+        <v>2146963</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2124048</v>
+        <v>2184620</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2138441</v>
+        <v>2186523</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2139582</v>
+        <v>2186526</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2147447</v>
+        <v>2186527</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -897,17 +897,17 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2147448</v>
+        <v>2200260</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EDITADO</t>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2147449</v>
+        <v>2200680</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2166981</v>
+        <v>2200681</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2184580</v>
+        <v>2203866</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2184581</v>
+        <v>2216295</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2185510</v>
+        <v>2216299</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2185865</v>
+        <v>2216301</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2185866</v>
+        <v>2217834</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2185867</v>
+        <v>2218149</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2185868</v>
+        <v>2220822</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2190686</v>
+        <v>2220824</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2190703</v>
+        <v>2220826</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2190836</v>
+        <v>2220827</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2190875</v>
+        <v>2220828</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2124063</v>
+        <v>2220829</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2138525</v>
+        <v>2022097</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2138756</v>
+        <v>2082751</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2138757</v>
+        <v>2137822</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2138758</v>
+        <v>2137823</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2138759</v>
+        <v>2164991</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2153395</v>
+        <v>2200263</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2170523</v>
+        <v>2203867</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2184582</v>
+        <v>2208212</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2184583</v>
+        <v>2221297</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2187909</v>
+        <v>2221298</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2187910</v>
+        <v>2223557</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2187911</v>
+        <v>2223563</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -1167,17 +1167,17 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2187912</v>
+        <v>2223580</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EDITADO</t>
+          <t>SIN METODO</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2190701</v>
+        <v>2155901</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -1187,17 +1187,17 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2190713</v>
+        <v>2155902</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EDITADO</t>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2190722</v>
+        <v>2155904</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2190754</v>
+        <v>2220501</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2190758</v>
+        <v>2228825</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2190759</v>
+        <v>2228833</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2190761</v>
+        <v>2228844</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2192142</v>
+        <v>2228845</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2193589</v>
+        <v>2228883</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -1265,148 +1265,8 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>2193853</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>SIN METODO</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>2153781</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>2153782</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>2153783</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>2153784</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>2155905</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>2155906</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>2155907</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>2166799</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>2172285</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>2187914</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>2187915</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>2187916</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>2187917</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>EDITADO</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B96"/>
+  <autoFilter ref="A1:B82"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Cambiar Lotes/ListaMuestras.xlsx
+++ b/Cambiar Lotes/ListaMuestras.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$248</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2293671</v>
+        <v>1389760</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -467,7 +467,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2260490</v>
+        <v>1454173</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -477,16 +477,2456 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2252075</v>
+        <v>1454185</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1591394</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1598805</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>ERROR</t>
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1598818</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1598832</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1675373</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1811116</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1811120</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1992089</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2022081</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2022082</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2022098</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2052561</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2052563</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2073353</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2074274</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2088388</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2111533</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2111587</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2111614</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2111617</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2111620</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2131625</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2138401</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2175973</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2175974</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2175975</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2180895</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2189431</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2189438</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2189444</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2189451</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2190749</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2190750</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2190752</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2196587</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2196588</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2196589</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2196596</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2196789</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2196790</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2196934</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2211789</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2211851</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2211894</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2211938</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2211951</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2211963</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2211976</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2211978</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2212307</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2212342</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2212373</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2216529</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2216575</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2220528</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2220530</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2222446</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2222448</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2222450</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2226255</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2228120</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2232919</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2232920</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2233970</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2233972</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2233975</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2233977</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2233980</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2233984</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2233990</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2233996</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2234008</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2234044</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2234049</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2235566</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2235567</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2235836</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2237626</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2238308</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2238315</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2239245</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2241335</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2241336</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2241534</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2241542</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2241594</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2242254</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2242786</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2243810</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2243811</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2247249</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2258326</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2258473</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2258905</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2258958</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2261148</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2261230</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2261231</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2262919</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2265535</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2266880</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2267629</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2268249</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2268250</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2268251</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2268252</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2268253</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2268369</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2268370</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2269475</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2269513</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>2270603</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2270778</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2270779</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>2270806</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2271466</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2272601</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2272602</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2272603</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>2276740</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>2276840</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>2276845</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2276847</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2276848</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2276850</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2276851</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2276852</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2276854</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>2276857</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>2276858</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2276859</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2276972</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2277378</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2277379</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2277380</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2277430</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2277431</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2278667</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2279250</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2279701</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2279725</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2280406</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2280440</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2280441</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2280442</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2280443</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2280444</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2280445</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2280501</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2280558</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2280711</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2280712</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2281024</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2281744</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2281183</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2268854</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2268856</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2282157</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2282295</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2282345</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2282349</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2282424</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2282868</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2282896</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2282923</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2283180</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2283182</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>2283995</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>2284066</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>2282930</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>2284135</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>2284148</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>2284150</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>2284161</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2284208</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>2284209</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>2284497</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>2284499</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>2284500</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>2284501</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>2284502</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>2284503</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>2284504</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>2284505</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>2284507</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>2284560</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>2284734</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>2284735</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>2284736</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>2284738</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>2284740</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>2284742</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>2285699</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2286754</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2286778</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2287857</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2289063</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2289396</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2290045</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2290154</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2290303</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2290380</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2291269</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2291281</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2291306</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2291313</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2291345</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>2291824</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>2291922</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>2293040</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>2293045</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>2293046</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>2293047</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>2293050</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>2293092</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>2293093</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>2293094</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>2293227</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>2293398</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>2293870</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>2297392</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>2298204</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>2298205</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>2298261</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2299197</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>2299368</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>2299369</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>2299370</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2299374</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>2300117</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>2300525</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2300526</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2301158</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>2301954</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>2303561</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>2304924</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>2305150</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>2305151</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2305152</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>2305153</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>2306120</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>2306587</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>2307638</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>2307888</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B4"/>
+  <autoFilter ref="A1:B248"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Cambiar Lotes/ListaMuestras.xlsx
+++ b/Cambiar Lotes/ListaMuestras.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$212</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,10 +52,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -64,7 +77,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -427,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,17 +457,17 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2361247</v>
+        <v>1389785</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EDITADO</t>
+          <t>SIN METODO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2362489</v>
+        <v>1973971</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -464,7 +477,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2357784</v>
+        <v>2076188</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -474,7 +487,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2357783</v>
+        <v>2190743</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -484,7 +497,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2355601</v>
+        <v>2211738</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -494,7 +507,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2353193</v>
+        <v>2211741</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -504,7 +517,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2352575</v>
+        <v>2211744</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -514,7 +527,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2352061</v>
+        <v>2211929</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -524,7 +537,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2352031</v>
+        <v>2212425</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -534,7 +547,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2352029</v>
+        <v>2212469</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -544,7 +557,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2351952</v>
+        <v>2238318</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -554,7 +567,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2350667</v>
+        <v>2263192</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -564,7 +577,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2350653</v>
+        <v>2263193</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -574,7 +587,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2344995</v>
+        <v>2263194</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -584,7 +597,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2344994</v>
+        <v>2263195</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -594,7 +607,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2343526</v>
+        <v>2263196</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -604,7 +617,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2343525</v>
+        <v>2263197</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -614,7 +627,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2343524</v>
+        <v>2263332</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -624,7 +637,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2343520</v>
+        <v>2263333</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -634,7 +647,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1598790</v>
+        <v>2263334</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -644,7 +657,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1598807</v>
+        <v>2263335</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -654,7 +667,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1598820</v>
+        <v>2263337</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -664,7 +677,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2102278</v>
+        <v>2263338</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -674,7 +687,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2190747</v>
+        <v>2263339</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -684,7 +697,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2198498</v>
+        <v>2263340</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -694,7 +707,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2238316</v>
+        <v>2263341</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -704,7 +717,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2262684</v>
+        <v>2263342</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -714,7 +727,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2262685</v>
+        <v>2263343</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -724,7 +737,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2298262</v>
+        <v>2263344</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -734,7 +747,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2305685</v>
+        <v>2263460</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -744,7 +757,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2309961</v>
+        <v>2263461</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -754,7 +767,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2316445</v>
+        <v>2263462</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -764,7 +777,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2316491</v>
+        <v>2263464</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -774,7 +787,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2316493</v>
+        <v>2263466</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -784,7 +797,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2316505</v>
+        <v>2263468</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -794,7 +807,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2320996</v>
+        <v>2263481</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -804,7 +817,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2320998</v>
+        <v>2263482</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -814,7 +827,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2321001</v>
+        <v>2263483</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -824,7 +837,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2321004</v>
+        <v>2263484</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -834,7 +847,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2321006</v>
+        <v>2263486</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -844,7 +857,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2321008</v>
+        <v>2263487</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -854,7 +867,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2321009</v>
+        <v>2263489</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -864,7 +877,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2321011</v>
+        <v>2263490</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -874,7 +887,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2321015</v>
+        <v>2263491</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -884,7 +897,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2322191</v>
+        <v>2263492</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -894,7 +907,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2331729</v>
+        <v>2263493</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -904,7 +917,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2332735</v>
+        <v>2263494</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -914,7 +927,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2339315</v>
+        <v>2263947</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -924,7 +937,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2339318</v>
+        <v>2263948</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -934,7 +947,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2339320</v>
+        <v>2263949</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -944,7 +957,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2339323</v>
+        <v>2263950</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -954,7 +967,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2339327</v>
+        <v>2263951</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -964,7 +977,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2339331</v>
+        <v>2263952</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -974,7 +987,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2339334</v>
+        <v>2265255</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -984,7 +997,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2339337</v>
+        <v>2265256</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -994,7 +1007,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2339339</v>
+        <v>2265257</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1004,7 +1017,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2339746</v>
+        <v>2265258</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1014,7 +1027,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2342507</v>
+        <v>2265259</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1024,7 +1037,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2342508</v>
+        <v>2265260</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1034,7 +1047,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2342583</v>
+        <v>2265262</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1044,7 +1057,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2343166</v>
+        <v>2265263</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1054,7 +1067,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2343167</v>
+        <v>2265264</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1064,7 +1077,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2343168</v>
+        <v>2265265</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1072,8 +1085,1403 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2265268</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2265271</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2281312</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2284593</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2284594</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2284595</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2284599</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2284602</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2287707</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2294027</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2303601</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2303602</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2304404</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2304406</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2305678</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2305687</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2305688</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2305689</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2305690</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2305694</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2305695</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2305696</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2318970</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2318971</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2320112</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2320113</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2320114</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2320115</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2320116</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2320117</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2321548</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2321549</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2321550</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2321552</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2321553</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2321554</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2324962</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2324967</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2339461</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2340026</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2341396</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2341397</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2341398</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2342091</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2343532</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2343534</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2343535</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2343536</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2343537</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2343538</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2343539</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>2343540</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2343541</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2343542</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>2345017</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2346651</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2346680</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2346723</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2348502</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>2349738</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>2350414</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>2350417</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2350421</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2350424</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2350428</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2350430</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2350431</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2350669</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>2350672</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>2354809</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2354817</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2354823</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2354826</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2354827</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2354828</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2354829</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2355534</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2355535</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2355537</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2355785</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2355786</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2357370</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2357371</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2357409</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2357411</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2359356</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2359357</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2359358</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2359360</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2359361</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2359362</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2359364</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2359365</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2359366</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2359369</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2359370</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2359371</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2359561</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2361538</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2361540</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2361541</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2361543</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2361544</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2361545</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2362915</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2363054</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2363055</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>2363056</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>2363057</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>2363396</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>2363397</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>2363398</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>2363400</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>2363401</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2363402</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>2363404</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>2363405</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>2363406</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>2363407</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>2363408</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>2363409</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>2123962</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>2123964</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>2123991</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>2227552</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>2227558</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>2367541</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>2227553</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>2123966</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>2368063</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>2370430</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>2370738</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>2370739</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2370740</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2372763</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2372762</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2372761</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2372760</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2372758</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2372756</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2372754</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2373099</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2375339</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2375236</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2375235</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2375234</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2375239</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>2371907</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B64"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:B212"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Cambiar Lotes/ListaMuestras.xlsx
+++ b/Cambiar Lotes/ListaMuestras.xlsx
@@ -2399,6 +2399,11 @@
       <c r="A196" t="n">
         <v>2370738</v>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">

--- a/Cambiar Lotes/ListaMuestras.xlsx
+++ b/Cambiar Lotes/ListaMuestras.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,566 +457,296 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2421201</v>
+        <v>2403938</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2421202</v>
+        <v>2403939</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2421203</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
+        <v>2404240</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2421204</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
+        <v>2404241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2421205</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
+        <v>2404242</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2421208</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
+        <v>2404243</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2421210</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
+        <v>2404244</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2421211</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
+        <v>2404359</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2421212</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
+        <v>2404361</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2421213</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
+        <v>2404362</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2421214</v>
+        <v>2404363</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2421215</v>
+        <v>2404364</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2421216</v>
+        <v>2404365</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2421217</v>
+        <v>2404366</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2421218</v>
+        <v>2404367</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2421219</v>
+        <v>2404368</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2421220</v>
+        <v>2404369</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2421221</v>
+        <v>2404370</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2421222</v>
+        <v>2404371</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2421223</v>
+        <v>2404372</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2421224</v>
+        <v>2404373</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2421225</v>
+        <v>2404374</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2421226</v>
+        <v>2404375</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2421227</v>
+        <v>2404376</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2421228</v>
+        <v>2404377</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2421229</v>
+        <v>2404378</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2421230</v>
+        <v>2404379</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2421231</v>
+        <v>2404380</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2421232</v>
+        <v>2404381</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2421233</v>
+        <v>2404382</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2421234</v>
+        <v>2404383</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2421235</v>
+        <v>2404424</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2421236</v>
+        <v>2404425</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>2421237</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>2421238</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>2421239</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>2421240</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>2421241</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>2421242</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>2421243</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>2421247</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>2421248</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>2421249</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>2421252</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>2421253</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>2421255</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>2421256</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>2421257</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>2421258</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>2421259</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>2421264</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>2421266</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>2421267</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>2421269</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>2421271</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>2421272</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>LISTA REPROCESADA</t>
+          <t>ANALISIS YA EXISTE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B57"/>
+  <autoFilter ref="A1:B34"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Cambiar Lotes/ListaMuestras.xlsx
+++ b/Cambiar Lotes/ListaMuestras.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$264</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,296 +457,2636 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2403938</v>
+        <v>1769063</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2403939</v>
+        <v>1973986</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2404240</v>
+        <v>2034418</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2404241</v>
+        <v>2034419</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2404242</v>
+        <v>2034420</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2404243</v>
+        <v>2034421</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2404244</v>
+        <v>2034422</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2404359</v>
+        <v>2034423</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2404361</v>
+        <v>2068792</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2404362</v>
+        <v>2084531</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2404363</v>
+        <v>2175776</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2404364</v>
+        <v>2175777</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2404365</v>
+        <v>2175778</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2404366</v>
+        <v>2175779</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2404367</v>
+        <v>2175780</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2404368</v>
+        <v>2175781</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2404369</v>
+        <v>2320099</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2404370</v>
+        <v>2320100</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2404371</v>
+        <v>2320101</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2404372</v>
+        <v>2320102</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2404373</v>
+        <v>2320103</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2404374</v>
+        <v>2320104</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2404375</v>
+        <v>2320105</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2404376</v>
+        <v>2320106</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2404377</v>
+        <v>2320107</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2404378</v>
+        <v>2320108</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2404379</v>
+        <v>2320109</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2404380</v>
+        <v>2320110</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2404381</v>
+        <v>2320136</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2404382</v>
+        <v>2320137</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2404383</v>
+        <v>2320138</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2404424</v>
+        <v>2320139</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2404425</v>
+        <v>2320140</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ANALISIS YA EXISTE</t>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2320141</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2320280</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2320281</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2320282</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2320283</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2320284</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2320285</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2320286</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2320287</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2320288</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2320289</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2320290</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2320291</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2321660</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2321661</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2321662</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2321663</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2321664</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2321665</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2336151</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2349677</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2360073</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2362863</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2367064</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2367065</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2367066</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2367067</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2367068</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2376322</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2376323</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2376330</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2380371</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2380372</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2380373</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2380374</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2380376</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2380377</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2380437</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2380439</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2380440</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2380441</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2380442</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2380444</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2380547</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2380551</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2380553</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2380555</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2380557</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2380559</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2380563</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2380564</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2380565</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2380567</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2380568</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2380569</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2380580</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2380581</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2380582</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2380584</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2380585</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2380587</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2380591</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2380592</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2380593</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2380594</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2380596</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2380597</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2380631</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2380632</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2380633</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2380634</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2380635</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2380636</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2380637</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2380638</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2380639</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2380640</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2380641</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2380642</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2380644</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2380645</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>2380646</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2380648</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2380649</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>2380650</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2380654</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2380655</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2380656</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2380657</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>2380658</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>2380660</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>2380661</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2380663</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2380664</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2380665</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2380666</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2380667</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2380670</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>2380671</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>2380672</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2380673</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2380674</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2380675</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2380695</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2380698</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2380701</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2380703</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2380706</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2380708</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2380720</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2380721</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2380722</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2380723</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2380724</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2380725</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2380726</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2380727</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2380728</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2380729</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2380730</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2380731</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2380758</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2380759</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2380760</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2380761</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2380763</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2380764</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2380819</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2380820</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2380821</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2380822</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2380823</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2380824</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2380829</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2380830</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2380831</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2380832</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>2380833</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>2380834</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>2380873</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>2380874</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>2380875</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>2380876</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>2380877</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2380878</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>2425134</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>2443610</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>2444547</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>2450873</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>2450874</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>2450875</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>2450876</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>2451673</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>2451674</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>2453552</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>2453712</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>2453713</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>2453714</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>2453715</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>2453716</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>2453717</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>2453718</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>2453720</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2453768</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2453769</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2453770</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2453771</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2453780</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2453781</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2453782</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2453783</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2453784</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2453785</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2453786</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2453787</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2453788</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2453789</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>2453790</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>2453791</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>2453792</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>2453793</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>2453794</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>2453795</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>2453796</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>2453797</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>2453798</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>2453800</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>2453802</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>2453803</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>2453804</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>2453805</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>2453806</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>2453807</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>2453808</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2453809</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>2454209</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>2455282</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>2458794</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2464095</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>2464230</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>2464234</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2309589</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2309570</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>2320509</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>1913239</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>2467863</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>2467864</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>2467865</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2467866</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>2467867</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>2467868</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>2467941</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>2467944</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>2467948</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>2467950</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>2467952</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>2467954</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>2468117</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>2468118</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>2468119</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>2468120</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>2468121</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>2468122</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>2468649</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>2468684</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>2468685</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>2468686</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>2468687</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>2468688</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>2468689</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>EDITADO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B34"/>
+  <autoFilter ref="A1:B264"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>